--- a/technology_surveys/045_smart_checkout_technology_application_form--technology_surveys.xlsx
+++ b/technology_surveys/045_smart_checkout_technology_application_form--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_likely',_'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'very_likely', 'label': 'very_likely'}</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_likely',_'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_likely', 'label': 'somewhat_likely'}</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'not_likely',_'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'not_likely', 'label': 'not_likely'}</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'operational_needs_1',_'label':_'operational_needs_1'}</t>
+          <t>operational_needs_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'operational_needs_1', 'label': 'operational_needs_1'}</t>
+          <t>operational needs 1</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'operational_needs_2',_'label':_'operational_needs_2'}</t>
+          <t>operational_needs_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'operational_needs_2', 'label': 'operational_needs_2'}</t>
+          <t>operational needs 2</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'very_good',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'very_good', 'label': 'very_good'}</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_good',_'label':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_good', 'label': 'somewhat_good'}</t>
+          <t>somewhat good</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'not_good',_'label':_'not_good'}</t>
+          <t>not_good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'not_good', 'label': 'not_good'}</t>
+          <t>not good</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'approved', 'label': 'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'rejected',_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'rejected', 'label': 'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
